--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_49.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3591049.502986135</v>
+        <v>3584160.294843635</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10030081.59640416</v>
+        <v>10029293.6368082</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10030081.59640416</v>
+        <v>10029293.6368082</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11583356.11428798</v>
+        <v>11583384.08918488</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +672,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>40.59665008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>127.4351591877375</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -745,13 +745,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>141.7804375265674</v>
       </c>
       <c r="G3" t="n">
-        <v>308.4311513056531</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>32.58699138541447</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>127.4351591877375</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>233.2097814359891</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>147.4295318620688</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>386</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1027,7 +1027,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>386</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>32.58699138541447</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>131.3159591877375</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1264,16 +1264,16 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>312.3673862446502</v>
       </c>
       <c r="V9" t="n">
-        <v>152.472173930159</v>
+        <v>387</v>
       </c>
       <c r="W9" t="n">
-        <v>386</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>386</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1380,13 +1380,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>53.75737228701621</v>
+        <v>61.60356367243072</v>
       </c>
       <c r="H11" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>7.846191385414503</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1447,7 +1447,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>62.67776252544269</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900539</v>
       </c>
       <c r="T12" t="n">
         <v>55.35776521751382</v>
@@ -1617,7 +1617,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>53.75737228701621</v>
+        <v>61.60356367243072</v>
       </c>
       <c r="H14" t="n">
         <v>58.00965870352741</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>7.846191385414608</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>144.8481678023229</v>
@@ -1684,7 +1684,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1744,13 +1744,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X15" t="n">
-        <v>132.5405019708301</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>49.39139276613435</v>
+        <v>112.069155291577</v>
       </c>
     </row>
     <row r="16">
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>7.846191385414608</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>144.8481678023229</v>
@@ -1899,7 +1899,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V17" t="n">
-        <v>279.8510241668239</v>
+        <v>287.6972155522382</v>
       </c>
       <c r="W17" t="n">
         <v>288.3734759809475</v>
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>80.50967533902158</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1981,10 +1981,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>82.37314290982852</v>
+        <v>145.0509054352711</v>
       </c>
       <c r="X18" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
         <v>49.39139276613435</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>7.846191385414503</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>7.846191385414608</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2161,19 +2161,19 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>80.50967533902158</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>73.04152018756581</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>65.85585008894192</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>7.846191385414608</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2410,10 +2410,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>195.5513766340942</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2446,10 +2446,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U24" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V24" t="n">
         <v>64.51066719152016</v>
@@ -2638,10 +2638,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>70.00566530353007</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2680,10 +2680,10 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S27" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429564</v>
       </c>
       <c r="U27" t="n">
         <v>50.21035976018675</v>
@@ -2802,13 +2802,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>61.60356367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H29" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2914,13 +2914,13 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>262.0138729201192</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S30" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T30" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429564</v>
       </c>
       <c r="U30" t="n">
         <v>50.21035976018675</v>
@@ -3039,13 +3039,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>61.60356367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>73.77767497096195</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>86.93822665041533</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>7.846191385414503</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>242.2818334606677</v>
+        <v>250.1280248460822</v>
       </c>
       <c r="Y35" t="n">
         <v>161.3174326828064</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>62.67776252544257</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3385,16 +3385,16 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T36" t="n">
-        <v>294.9562626524769</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
         <v>50.21035976018675</v>
@@ -3516,10 +3516,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
-        <v>65.85585008894192</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>64.74007562774005</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
         <v>50.21035976018675</v>
@@ -3640,7 +3640,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>145.0509054352711</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X39" t="n">
         <v>69.86273944538755</v>
@@ -3750,7 +3750,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>61.60356367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
         <v>58.00965870352741</v>
@@ -3792,7 +3792,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>299.2212965486107</v>
+        <v>307.0674879340252</v>
       </c>
       <c r="V41" t="n">
         <v>279.8510241668239</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>62.67776252544257</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900539</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -4054,7 +4054,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>11.09991244551929</v>
+        <v>84.14143263308509</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>392.8251739264735</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>145.4463380542246</v>
+        <v>112.5301851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>95.47201659665494</v>
+        <v>62.55586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>85.02842494024101</v>
+        <v>52.11227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>80.62106170097975</v>
+        <v>47.70490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>75.68204280399807</v>
+        <v>42.76588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>71.88671726155745</v>
+        <v>38.97056434699738</v>
       </c>
       <c r="H2" t="n">
         <v>30.88</v>
@@ -4330,13 +4330,13 @@
         <v>30.88</v>
       </c>
       <c r="M2" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="N2" t="n">
         <v>397.5800000000002</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>779.7200000000001</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1161.86</v>
       </c>
       <c r="P2" t="n">
         <v>1161.86</v>
@@ -4348,25 +4348,25 @@
         <v>1544</v>
       </c>
       <c r="S2" t="n">
-        <v>1448.193769896644</v>
+        <v>1415.277616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1259.632576231427</v>
+        <v>1226.716423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1007.893892848992</v>
+        <v>974.9777399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>775.7211411653319</v>
+        <v>742.8049882507718</v>
       </c>
       <c r="W2" t="n">
-        <v>534.9398522956878</v>
+        <v>502.0236993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>340.7157780929932</v>
+        <v>307.7996251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>228.2739268982392</v>
+        <v>195.3577739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.2695195792149</v>
+        <v>722.4419790837811</v>
       </c>
       <c r="C3" t="n">
-        <v>897.2695195792149</v>
+        <v>722.4419790837811</v>
       </c>
       <c r="D3" t="n">
-        <v>897.2695195792149</v>
+        <v>722.4419790837811</v>
       </c>
       <c r="E3" t="n">
-        <v>897.2695195792149</v>
+        <v>722.4419790837811</v>
       </c>
       <c r="F3" t="n">
-        <v>897.2695195792149</v>
+        <v>579.2294159256322</v>
       </c>
       <c r="G3" t="n">
-        <v>585.7229020987572</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="H3" t="n">
         <v>250.1995817084329</v>
@@ -4421,31 +4421,31 @@
         <v>1186.312420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1186.312420368536</v>
+        <v>1011.484879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1037.551008962092</v>
+        <v>862.723468466658</v>
       </c>
       <c r="S3" t="n">
-        <v>970.3146453614744</v>
+        <v>795.4871048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>964.9027613033796</v>
+        <v>790.0752208079458</v>
       </c>
       <c r="U3" t="n">
-        <v>964.6902766971303</v>
+        <v>789.8627362016965</v>
       </c>
       <c r="V3" t="n">
-        <v>950.0330371097363</v>
+        <v>775.2054966143024</v>
       </c>
       <c r="W3" t="n">
-        <v>917.3328927563741</v>
+        <v>742.5053522609403</v>
       </c>
       <c r="X3" t="n">
-        <v>897.2695195792149</v>
+        <v>722.4419790837811</v>
       </c>
       <c r="Y3" t="n">
-        <v>897.2695195792149</v>
+        <v>722.4419790837811</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>315.9074818566527</v>
+        <v>816.9213798890015</v>
       </c>
       <c r="C4" t="n">
-        <v>441.9094876750885</v>
+        <v>942.9233857074373</v>
       </c>
       <c r="D4" t="n">
-        <v>555.2286318000886</v>
+        <v>1056.242529832437</v>
       </c>
       <c r="E4" t="n">
-        <v>555.2286318000886</v>
+        <v>1056.242529832437</v>
       </c>
       <c r="F4" t="n">
-        <v>679.5896043920241</v>
+        <v>1180.603502424373</v>
       </c>
       <c r="G4" t="n">
-        <v>679.5896043920241</v>
+        <v>1180.603502424373</v>
       </c>
       <c r="H4" t="n">
-        <v>849.1061895514216</v>
+        <v>1180.603502424373</v>
       </c>
       <c r="I4" t="n">
-        <v>1070.239068487504</v>
+        <v>1180.603502424373</v>
       </c>
       <c r="J4" t="n">
-        <v>1431.322809139956</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="K4" t="n">
         <v>1541.687243076824</v>
@@ -4506,25 +4506,25 @@
         <v>30.88</v>
       </c>
       <c r="S4" t="n">
-        <v>68.13025509417312</v>
+        <v>30.88</v>
       </c>
       <c r="T4" t="n">
-        <v>68.13025509417312</v>
+        <v>48.62708508089804</v>
       </c>
       <c r="U4" t="n">
-        <v>68.13025509417312</v>
+        <v>295.1782777191847</v>
       </c>
       <c r="V4" t="n">
-        <v>68.13025509417312</v>
+        <v>493.9996706051306</v>
       </c>
       <c r="W4" t="n">
-        <v>68.13025509417312</v>
+        <v>665.890588864808</v>
       </c>
       <c r="X4" t="n">
-        <v>204.4981811776204</v>
+        <v>816.9213798890015</v>
       </c>
       <c r="Y4" t="n">
-        <v>315.9074818566527</v>
+        <v>816.9213798890015</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.5301851396645</v>
+        <v>145.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.55586368209485</v>
+        <v>95.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.11227202568092</v>
+        <v>85.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.70490878641967</v>
+        <v>80.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.76588988943799</v>
+        <v>75.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.97056434699738</v>
+        <v>71.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>30.88</v>
+        <v>63.79615291456007</v>
       </c>
       <c r="I5" t="n">
         <v>30.88</v>
@@ -4585,25 +4585,25 @@
         <v>1544</v>
       </c>
       <c r="S5" t="n">
-        <v>1415.277616982083</v>
+        <v>1448.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1226.716423316867</v>
+        <v>1259.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.9777399344323</v>
+        <v>1007.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.8049882507718</v>
+        <v>775.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>502.0236993811278</v>
+        <v>534.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7996251784331</v>
+        <v>340.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.3577739836791</v>
+        <v>228.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.88</v>
+        <v>508.8285532697941</v>
       </c>
       <c r="C6" t="n">
-        <v>30.88</v>
+        <v>508.8285532697941</v>
       </c>
       <c r="D6" t="n">
-        <v>30.88</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="E6" t="n">
-        <v>30.88</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="F6" t="n">
-        <v>30.88</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="G6" t="n">
         <v>30.88</v>
@@ -4661,28 +4661,28 @@
         <v>1186.312420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>796.4134304695458</v>
+        <v>1037.551008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>729.1770668689284</v>
+        <v>970.3146453614744</v>
       </c>
       <c r="T6" t="n">
-        <v>723.7651828108336</v>
+        <v>964.9027613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>333.8661929118437</v>
+        <v>964.6902766971303</v>
       </c>
       <c r="V6" t="n">
-        <v>319.2089533244496</v>
+        <v>950.0330371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>286.5088089710875</v>
+        <v>917.3328927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>266.4454357939284</v>
+        <v>897.2695195792149</v>
       </c>
       <c r="Y6" t="n">
-        <v>266.4454357939284</v>
+        <v>897.2695195792149</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>597.9816666711695</v>
+        <v>937.4361738414277</v>
       </c>
       <c r="C7" t="n">
-        <v>597.9816666711695</v>
+        <v>937.4361738414277</v>
       </c>
       <c r="D7" t="n">
-        <v>597.9816666711695</v>
+        <v>937.4361738414277</v>
       </c>
       <c r="E7" t="n">
-        <v>597.9816666711695</v>
+        <v>959.47062348829</v>
       </c>
       <c r="F7" t="n">
-        <v>722.342639263105</v>
+        <v>959.47062348829</v>
       </c>
       <c r="G7" t="n">
-        <v>722.342639263105</v>
+        <v>959.47062348829</v>
       </c>
       <c r="H7" t="n">
-        <v>891.8592244225025</v>
+        <v>959.47062348829</v>
       </c>
       <c r="I7" t="n">
-        <v>1112.992103358585</v>
+        <v>1180.603502424373</v>
       </c>
       <c r="J7" t="n">
-        <v>1474.075844011037</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="K7" t="n">
         <v>1541.687243076824</v>
@@ -4746,22 +4746,22 @@
         <v>68.13025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>68.13025509417312</v>
+        <v>256.205934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>314.6814477324598</v>
+        <v>502.7571268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>314.6814477324598</v>
+        <v>502.7571268912646</v>
       </c>
       <c r="W7" t="n">
-        <v>486.5723659921372</v>
+        <v>674.648045150942</v>
       </c>
       <c r="X7" t="n">
-        <v>486.5723659921372</v>
+        <v>825.6788361751355</v>
       </c>
       <c r="Y7" t="n">
-        <v>597.9816666711695</v>
+        <v>825.6788361751355</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>145.4463380542246</v>
+        <v>112.6101851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>95.47201659665494</v>
+        <v>62.63586368209486</v>
       </c>
       <c r="D8" t="n">
-        <v>85.02842494024101</v>
+        <v>52.19227202568093</v>
       </c>
       <c r="E8" t="n">
-        <v>80.62106170097975</v>
+        <v>47.78490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>75.68204280399807</v>
+        <v>42.845889889438</v>
       </c>
       <c r="G8" t="n">
-        <v>71.88671726155745</v>
+        <v>39.05056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>63.79615291456007</v>
+        <v>30.96</v>
       </c>
       <c r="I8" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="J8" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="K8" t="n">
-        <v>397.5800000000002</v>
+        <v>414.09</v>
       </c>
       <c r="L8" t="n">
-        <v>779.7200000000001</v>
+        <v>797.2199999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>1161.86</v>
+        <v>1180.35</v>
       </c>
       <c r="N8" t="n">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="O8" t="n">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="P8" t="n">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="Q8" t="n">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="R8" t="n">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="S8" t="n">
-        <v>1448.193769896644</v>
+        <v>1415.357616982083</v>
       </c>
       <c r="T8" t="n">
-        <v>1259.632576231427</v>
+        <v>1226.796423316867</v>
       </c>
       <c r="U8" t="n">
-        <v>1007.893892848992</v>
+        <v>975.0577399344323</v>
       </c>
       <c r="V8" t="n">
-        <v>775.7211411653319</v>
+        <v>742.8849882507718</v>
       </c>
       <c r="W8" t="n">
-        <v>534.9398522956878</v>
+        <v>502.1036993811277</v>
       </c>
       <c r="X8" t="n">
-        <v>340.7157780929932</v>
+        <v>307.8796251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>228.2739268982392</v>
+        <v>195.4377739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="C9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="D9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="E9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="F9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="G9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="H9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="I9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="J9" t="n">
-        <v>154.8365201752989</v>
+        <v>154.916520175299</v>
       </c>
       <c r="K9" t="n">
-        <v>344.0293362696823</v>
+        <v>344.1093362696823</v>
       </c>
       <c r="L9" t="n">
-        <v>615.3797978648824</v>
+        <v>615.4597978648824</v>
       </c>
       <c r="M9" t="n">
-        <v>701.4603396077417</v>
+        <v>701.5403396077417</v>
       </c>
       <c r="N9" t="n">
-        <v>834.74062421531</v>
+        <v>834.82062421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1073.783075899029</v>
+        <v>1073.863075899029</v>
       </c>
       <c r="P9" t="n">
-        <v>1186.312420368536</v>
+        <v>1186.392420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1186.312420368536</v>
+        <v>1011.564879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1037.551008962092</v>
+        <v>862.8034684666579</v>
       </c>
       <c r="S9" t="n">
-        <v>970.3146453614744</v>
+        <v>795.5671048660405</v>
       </c>
       <c r="T9" t="n">
-        <v>964.9027613033796</v>
+        <v>790.1552208079457</v>
       </c>
       <c r="U9" t="n">
-        <v>964.6902766971303</v>
+        <v>474.6326084396122</v>
       </c>
       <c r="V9" t="n">
-        <v>810.6779797979798</v>
+        <v>83.72351753052129</v>
       </c>
       <c r="W9" t="n">
-        <v>420.7789898989899</v>
+        <v>51.02337317715914</v>
       </c>
       <c r="X9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="Y9" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>351.4304740328828</v>
+        <v>351.5104740328828</v>
       </c>
       <c r="C10" t="n">
-        <v>477.4324798513186</v>
+        <v>351.5104740328828</v>
       </c>
       <c r="D10" t="n">
-        <v>590.7516239763187</v>
+        <v>453.5897468611878</v>
       </c>
       <c r="E10" t="n">
-        <v>708.5805281877317</v>
+        <v>571.4186510726008</v>
       </c>
       <c r="F10" t="n">
-        <v>708.5805281877317</v>
+        <v>695.7796236645363</v>
       </c>
       <c r="G10" t="n">
-        <v>861.9870940746169</v>
+        <v>849.1861895514215</v>
       </c>
       <c r="H10" t="n">
-        <v>861.9870940746169</v>
+        <v>849.1861895514215</v>
       </c>
       <c r="I10" t="n">
-        <v>1070.239068487504</v>
+        <v>1070.319068487504</v>
       </c>
       <c r="J10" t="n">
-        <v>1431.322809139956</v>
+        <v>1431.402809139956</v>
       </c>
       <c r="K10" t="n">
-        <v>1541.687243076824</v>
+        <v>1541.767243076824</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.901760089168</v>
+        <v>1517.981760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1396.05164756134</v>
+        <v>1396.13164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.137430115194</v>
+        <v>1223.217430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>980.2631229646734</v>
+        <v>980.3431229646733</v>
       </c>
       <c r="P10" t="n">
-        <v>689.9117115219688</v>
+        <v>689.9917115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7811393749001</v>
+        <v>360.8611393749001</v>
       </c>
       <c r="R10" t="n">
-        <v>30.88</v>
+        <v>30.96</v>
       </c>
       <c r="S10" t="n">
-        <v>68.13025509417312</v>
+        <v>68.21025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>68.13025509417312</v>
+        <v>68.21025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>68.13025509417312</v>
+        <v>68.21025509417312</v>
       </c>
       <c r="V10" t="n">
-        <v>68.13025509417312</v>
+        <v>68.21025509417312</v>
       </c>
       <c r="W10" t="n">
-        <v>240.0211733538505</v>
+        <v>240.1011733538505</v>
       </c>
       <c r="X10" t="n">
-        <v>240.0211733538505</v>
+        <v>240.1011733538505</v>
       </c>
       <c r="Y10" t="n">
-        <v>351.4304740328828</v>
+        <v>351.5104740328828</v>
       </c>
     </row>
     <row r="11">
@@ -5023,10 +5023,10 @@
         <v>165.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>111.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>52.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I11" t="n">
         <v>44.8</v>
@@ -5035,22 +5035,22 @@
         <v>436.1091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>436.1091130376557</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>620.3511712710648</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="M11" t="n">
-        <v>1131.2</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="N11" t="n">
-        <v>1685.6</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2240</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>472.8582575464263</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C12" t="n">
-        <v>108.1108712378209</v>
+        <v>44.8</v>
       </c>
       <c r="D12" t="n">
-        <v>108.1108712378209</v>
+        <v>44.8</v>
       </c>
       <c r="E12" t="n">
-        <v>108.1108712378209</v>
+        <v>44.8</v>
       </c>
       <c r="F12" t="n">
-        <v>108.1108712378209</v>
+        <v>44.8</v>
       </c>
       <c r="G12" t="n">
-        <v>108.1108712378209</v>
+        <v>44.8</v>
       </c>
       <c r="H12" t="n">
         <v>44.8</v>
@@ -5135,28 +5135,28 @@
         <v>1200.232420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1000.965958457041</v>
+        <v>647.4306049216879</v>
       </c>
       <c r="S12" t="n">
-        <v>883.2245443513734</v>
+        <v>466.3783195781991</v>
       </c>
       <c r="T12" t="n">
-        <v>827.3076097882282</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5900746769285</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V12" t="n">
-        <v>711.4277845844838</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W12" t="n">
-        <v>628.2225897260712</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X12" t="n">
-        <v>557.6541660438616</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y12" t="n">
-        <v>507.7638703204935</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="13">
@@ -5169,16 +5169,16 @@
         <v>877.8366123122328</v>
       </c>
       <c r="C13" t="n">
-        <v>946.6278354584616</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D13" t="n">
-        <v>1010.446979583462</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E13" t="n">
-        <v>1078.775883794875</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F13" t="n">
-        <v>1153.63685638681</v>
+        <v>1161.347639059017</v>
       </c>
       <c r="G13" t="n">
         <v>1257.543422273696</v>
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4804881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>329.0011162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>268.052474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.1400603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.695990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G14" t="n">
         <v>103.3956148520479</v>
@@ -5269,10 +5269,10 @@
         <v>44.8</v>
       </c>
       <c r="J14" t="n">
-        <v>44.8</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>599.2</v>
+        <v>736.1520762183974</v>
       </c>
       <c r="L14" t="n">
         <v>736.1520762183974</v>
@@ -5293,28 +5293,28 @@
         <v>2240</v>
       </c>
       <c r="R14" t="n">
-        <v>2232.074554156147</v>
+        <v>2240</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.76327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.697029377473</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.453295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.775493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4891539265824</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.7600292188372</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.8131275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56.01203277325182</v>
+        <v>409.5473863086054</v>
       </c>
       <c r="C15" t="n">
         <v>44.8</v>
@@ -5387,13 +5387,13 @@
         <v>711.4277845844838</v>
       </c>
       <c r="W15" t="n">
-        <v>274.6872361907176</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X15" t="n">
-        <v>140.8079412706871</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y15" t="n">
-        <v>90.9176455473191</v>
+        <v>444.4529990826726</v>
       </c>
     </row>
     <row r="16">
@@ -5509,13 +5509,13 @@
         <v>436.1091130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>736.1520762183975</v>
+        <v>736.1520762183974</v>
       </c>
       <c r="L17" t="n">
-        <v>1290.552076218397</v>
+        <v>736.1520762183974</v>
       </c>
       <c r="M17" t="n">
-        <v>1801.400904947332</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="N17" t="n">
         <v>1801.400904947332</v>
@@ -5530,16 +5530,16 @@
         <v>2240</v>
       </c>
       <c r="R17" t="n">
-        <v>2232.074554156147</v>
+        <v>2240</v>
       </c>
       <c r="S17" t="n">
-        <v>2085.76327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1846.697029377473</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1544.453295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V17" t="n">
         <v>1261.775493301277</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.8582575464263</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C18" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="D18" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="E18" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="F18" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="G18" t="n">
-        <v>380.3233203903244</v>
+        <v>44.8</v>
       </c>
       <c r="H18" t="n">
         <v>44.8</v>
@@ -5624,13 +5624,13 @@
         <v>711.4277845844838</v>
       </c>
       <c r="W18" t="n">
-        <v>628.2225897260712</v>
+        <v>564.9117184882504</v>
       </c>
       <c r="X18" t="n">
-        <v>557.6541660438616</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.7638703204935</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>437.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C20" t="n">
-        <v>336.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D20" t="n">
-        <v>275.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E20" t="n">
-        <v>221.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F20" t="n">
-        <v>165.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G20" t="n">
-        <v>111.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H20" t="n">
-        <v>52.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I20" t="n">
         <v>44.8</v>
@@ -5761,34 +5761,34 @@
         <v>1501.357941766591</v>
       </c>
       <c r="P20" t="n">
-        <v>1801.400904947332</v>
+        <v>2055.757941766591</v>
       </c>
       <c r="Q20" t="n">
         <v>2240</v>
       </c>
       <c r="R20" t="n">
-        <v>2240</v>
+        <v>2232.074554156147</v>
       </c>
       <c r="S20" t="n">
-        <v>2093.688719391593</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T20" t="n">
-        <v>1854.622475221327</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U20" t="n">
-        <v>1552.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V20" t="n">
-        <v>1269.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W20" t="n">
-        <v>978.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X20" t="n">
-        <v>733.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y20" t="n">
-        <v>570.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="21">
@@ -5804,16 +5804,16 @@
         <v>461.6462247731745</v>
       </c>
       <c r="D21" t="n">
-        <v>380.3233203903244</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E21" t="n">
-        <v>380.3233203903244</v>
+        <v>387.8669114524009</v>
       </c>
       <c r="F21" t="n">
-        <v>380.3233203903244</v>
+        <v>44.8</v>
       </c>
       <c r="G21" t="n">
-        <v>380.3233203903244</v>
+        <v>44.8</v>
       </c>
       <c r="H21" t="n">
         <v>44.8</v>
@@ -5931,7 +5931,7 @@
         <v>44.8</v>
       </c>
       <c r="T22" t="n">
-        <v>183.3756791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U22" t="n">
         <v>372.7160891248845</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>437.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>336.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>275.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>221.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F23" t="n">
-        <v>165.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G23" t="n">
-        <v>111.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H23" t="n">
         <v>44.8</v>
@@ -5980,19 +5980,19 @@
         <v>44.8</v>
       </c>
       <c r="J23" t="n">
-        <v>436.1091130376557</v>
+        <v>44.8</v>
       </c>
       <c r="K23" t="n">
-        <v>436.1091130376557</v>
+        <v>599.2</v>
       </c>
       <c r="L23" t="n">
-        <v>620.3511712710648</v>
+        <v>1153.6</v>
       </c>
       <c r="M23" t="n">
-        <v>1131.2</v>
+        <v>1664.448828728935</v>
       </c>
       <c r="N23" t="n">
-        <v>1685.6</v>
+        <v>2218.848828728935</v>
       </c>
       <c r="O23" t="n">
         <v>2240</v>
@@ -6004,28 +6004,28 @@
         <v>2240</v>
       </c>
       <c r="R23" t="n">
-        <v>2240</v>
+        <v>2232.074554156147</v>
       </c>
       <c r="S23" t="n">
-        <v>2093.688719391593</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T23" t="n">
-        <v>1854.622475221327</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U23" t="n">
-        <v>1552.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V23" t="n">
-        <v>1269.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W23" t="n">
-        <v>978.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X23" t="n">
-        <v>733.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y23" t="n">
-        <v>570.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,25 +6035,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.8582575464263</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C24" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="D24" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="E24" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="F24" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="G24" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="H24" t="n">
-        <v>264.1195817084329</v>
+        <v>44.8</v>
       </c>
       <c r="I24" t="n">
         <v>44.8</v>
@@ -6089,22 +6089,22 @@
         <v>883.2245443513734</v>
       </c>
       <c r="T24" t="n">
-        <v>827.3076097882282</v>
+        <v>473.7722562528746</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5900746769285</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V24" t="n">
-        <v>711.4277845844838</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W24" t="n">
-        <v>628.2225897260712</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>557.6541660438616</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.7638703204935</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6114,13 +6114,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>870.1258296400258</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C25" t="n">
-        <v>946.6278354584616</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D25" t="n">
-        <v>1010.446979583462</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E25" t="n">
         <v>1078.775883794875</v>
@@ -6171,19 +6171,19 @@
         <v>183.3756791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>372.7160891248845</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>522.0374820108304</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W25" t="n">
-        <v>644.4284002705078</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X25" t="n">
-        <v>745.9591912947013</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y25" t="n">
-        <v>807.8684919737336</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="26">
@@ -6217,7 +6217,7 @@
         <v>44.8</v>
       </c>
       <c r="J26" t="n">
-        <v>436.1091130376557</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="K26" t="n">
         <v>620.3511712710648</v>
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>472.8582575464263</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C27" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="D27" t="n">
-        <v>461.6462247731745</v>
+        <v>44.8</v>
       </c>
       <c r="E27" t="n">
-        <v>115.512793235889</v>
+        <v>44.8</v>
       </c>
       <c r="F27" t="n">
         <v>44.8</v>
@@ -6323,25 +6323,25 @@
         <v>1000.965958457041</v>
       </c>
       <c r="S27" t="n">
-        <v>883.2245443513734</v>
+        <v>529.6891908160198</v>
       </c>
       <c r="T27" t="n">
-        <v>827.3076097882282</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5900746769285</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V27" t="n">
-        <v>711.4277845844838</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W27" t="n">
-        <v>628.2225897260712</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>557.6541660438616</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>507.7638703204935</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6445,10 +6445,10 @@
         <v>165.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3956148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H29" t="n">
-        <v>44.8</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I29" t="n">
         <v>44.8</v>
@@ -6457,22 +6457,22 @@
         <v>44.8</v>
       </c>
       <c r="K29" t="n">
-        <v>65.95117127106482</v>
+        <v>181.7520762183974</v>
       </c>
       <c r="L29" t="n">
-        <v>620.3511712710648</v>
+        <v>181.7520762183974</v>
       </c>
       <c r="M29" t="n">
-        <v>1131.2</v>
+        <v>692.6009049473324</v>
       </c>
       <c r="N29" t="n">
-        <v>1685.6</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="O29" t="n">
-        <v>1685.6</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>2240</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>407.4642417608302</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C30" t="n">
-        <v>396.2522089875785</v>
+        <v>44.8</v>
       </c>
       <c r="D30" t="n">
         <v>44.8</v>
@@ -6557,28 +6557,28 @@
         <v>1200.232420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>935.5719426714455</v>
+        <v>647.4306049216879</v>
       </c>
       <c r="S30" t="n">
-        <v>817.8305285657775</v>
+        <v>529.6891908160198</v>
       </c>
       <c r="T30" t="n">
-        <v>761.9135940026323</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U30" t="n">
-        <v>711.1960588913325</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V30" t="n">
-        <v>646.0337687988879</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W30" t="n">
-        <v>562.8285739404752</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X30" t="n">
-        <v>492.2601502582655</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y30" t="n">
-        <v>442.3698545348975</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="31">
@@ -6594,19 +6594,19 @@
         <v>954.3386181306686</v>
       </c>
       <c r="D31" t="n">
-        <v>1010.446979583462</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E31" t="n">
-        <v>1078.775883794875</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F31" t="n">
-        <v>1153.63685638681</v>
+        <v>1161.347639059017</v>
       </c>
       <c r="G31" t="n">
-        <v>1257.543422273696</v>
+        <v>1265.254204945903</v>
       </c>
       <c r="H31" t="n">
-        <v>1377.560007433093</v>
+        <v>1385.2707901053</v>
       </c>
       <c r="I31" t="n">
         <v>1549.192886369176</v>
@@ -6682,31 +6682,31 @@
         <v>165.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3956148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>44.8</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I32" t="n">
         <v>44.8</v>
       </c>
       <c r="J32" t="n">
-        <v>44.8</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>44.8</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>181.7520762183974</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>692.6009049473324</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N32" t="n">
-        <v>1247.000904947332</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1247.000904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P32" t="n">
         <v>1801.400904947332</v>
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>119.3229040110727</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C33" t="n">
-        <v>44.8</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D33" t="n">
-        <v>44.8</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E33" t="n">
-        <v>44.8</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="F33" t="n">
-        <v>44.8</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="G33" t="n">
         <v>44.8</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>870.1258296400258</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C34" t="n">
         <v>946.6278354584616</v>
@@ -6879,22 +6879,22 @@
         <v>44.8</v>
       </c>
       <c r="T34" t="n">
-        <v>175.6648964865979</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U34" t="n">
-        <v>372.7160891248845</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V34" t="n">
-        <v>522.0374820108304</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W34" t="n">
-        <v>644.4284002705078</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X34" t="n">
-        <v>745.9591912947013</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y34" t="n">
-        <v>807.8684919737336</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="35">
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>437.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>336.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>275.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>221.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>165.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>111.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>52.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I35" t="n">
         <v>44.8</v>
@@ -6934,13 +6934,13 @@
         <v>990.5091130376557</v>
       </c>
       <c r="L35" t="n">
-        <v>1544.909113037656</v>
+        <v>1174.751171271065</v>
       </c>
       <c r="M35" t="n">
-        <v>1544.909113037656</v>
+        <v>1685.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2099.309113037656</v>
+        <v>2240</v>
       </c>
       <c r="O35" t="n">
         <v>2240</v>
@@ -6970,10 +6970,10 @@
         <v>978.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>733.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y35" t="n">
-        <v>570.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>56.01203277325182</v>
+        <v>119.3229040110726</v>
       </c>
       <c r="C36" t="n">
-        <v>44.8</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="D36" t="n">
-        <v>44.8</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="E36" t="n">
-        <v>44.8</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="F36" t="n">
         <v>44.8</v>
@@ -7028,31 +7028,31 @@
         <v>1200.232420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1025.404879873102</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>826.1384179616076</v>
+        <v>647.4306049216879</v>
       </c>
       <c r="S36" t="n">
-        <v>708.3970038559396</v>
+        <v>529.6891908160198</v>
       </c>
       <c r="T36" t="n">
-        <v>410.4613850150538</v>
+        <v>473.7722562528746</v>
       </c>
       <c r="U36" t="n">
-        <v>359.743849903754</v>
+        <v>423.0547211415748</v>
       </c>
       <c r="V36" t="n">
-        <v>294.5815598113094</v>
+        <v>357.8924310491302</v>
       </c>
       <c r="W36" t="n">
-        <v>211.3763649528968</v>
+        <v>274.6872361907176</v>
       </c>
       <c r="X36" t="n">
-        <v>140.8079412706871</v>
+        <v>204.1188125085079</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.9176455473191</v>
+        <v>154.2285167851399</v>
       </c>
     </row>
     <row r="37">
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.8366123122328</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C37" t="n">
         <v>946.6278354584616</v>
@@ -7159,31 +7159,31 @@
         <v>111.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.8</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.8</v>
       </c>
       <c r="J38" t="n">
-        <v>436.1091130376557</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="K38" t="n">
-        <v>990.5091130376557</v>
+        <v>620.3511712710648</v>
       </c>
       <c r="L38" t="n">
-        <v>1247.000904947332</v>
+        <v>1174.751171271065</v>
       </c>
       <c r="M38" t="n">
-        <v>1247.000904947332</v>
+        <v>1685.6</v>
       </c>
       <c r="N38" t="n">
-        <v>1247.000904947332</v>
+        <v>1685.6</v>
       </c>
       <c r="O38" t="n">
-        <v>1247.000904947332</v>
+        <v>2240</v>
       </c>
       <c r="P38" t="n">
-        <v>1801.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="Q38" t="n">
         <v>2240</v>
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>56.01203277325182</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C39" t="n">
-        <v>44.8</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D39" t="n">
-        <v>44.8</v>
+        <v>110.194015785596</v>
       </c>
       <c r="E39" t="n">
         <v>44.8</v>
@@ -7274,22 +7274,22 @@
         <v>883.2245443513734</v>
       </c>
       <c r="T39" t="n">
-        <v>473.7722562528746</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U39" t="n">
-        <v>423.0547211415748</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V39" t="n">
-        <v>357.8924310491302</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W39" t="n">
-        <v>211.3763649528968</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X39" t="n">
-        <v>140.8079412706871</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.9176455473191</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="40">
@@ -7299,31 +7299,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.1258296400258</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.6278354584616</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.446979583462</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.775883794875</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.63685638681</v>
+        <v>1161.347639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.543422273696</v>
+        <v>1265.254204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.560007433093</v>
+        <v>1385.2707901053</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.192886369176</v>
+        <v>1556.903669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.776627021628</v>
+        <v>1868.487409693834</v>
       </c>
       <c r="K40" t="n">
         <v>1921.641060958496</v>
@@ -7368,7 +7368,7 @@
         <v>753.6699739669083</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.8684919737336</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>437.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>336.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>275.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>221.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>165.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G41" t="n">
         <v>103.3956148520479</v>
@@ -7402,25 +7402,25 @@
         <v>44.8</v>
       </c>
       <c r="J41" t="n">
-        <v>65.95117127106482</v>
+        <v>181.7520762183975</v>
       </c>
       <c r="K41" t="n">
-        <v>620.3511712710648</v>
+        <v>736.1520762183975</v>
       </c>
       <c r="L41" t="n">
-        <v>1174.751171271065</v>
+        <v>1290.552076218397</v>
       </c>
       <c r="M41" t="n">
-        <v>1685.6</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="N41" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2240</v>
@@ -7435,19 +7435,19 @@
         <v>1854.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1552.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1269.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>978.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X41" t="n">
-        <v>733.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y41" t="n">
-        <v>570.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119.3229040110726</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C42" t="n">
-        <v>108.1108712378208</v>
+        <v>44.8</v>
       </c>
       <c r="D42" t="n">
-        <v>108.1108712378208</v>
+        <v>44.8</v>
       </c>
       <c r="E42" t="n">
-        <v>108.1108712378208</v>
+        <v>44.8</v>
       </c>
       <c r="F42" t="n">
-        <v>108.1108712378208</v>
+        <v>44.8</v>
       </c>
       <c r="G42" t="n">
-        <v>108.1108712378208</v>
+        <v>44.8</v>
       </c>
       <c r="H42" t="n">
-        <v>108.1108712378208</v>
+        <v>44.8</v>
       </c>
       <c r="I42" t="n">
         <v>44.8</v>
@@ -7508,25 +7508,25 @@
         <v>647.4306049216879</v>
       </c>
       <c r="S42" t="n">
-        <v>529.6891908160198</v>
+        <v>466.3783195781991</v>
       </c>
       <c r="T42" t="n">
-        <v>473.7722562528746</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U42" t="n">
-        <v>423.0547211415748</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V42" t="n">
-        <v>357.8924310491302</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>274.6872361907176</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>204.1188125085079</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.2285167851399</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7536,31 +7536,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.8366123122328</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C43" t="n">
-        <v>954.3386181306686</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D43" t="n">
-        <v>1018.157762255669</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1086.486666467082</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1161.347639059017</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1265.254204945903</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H43" t="n">
-        <v>1385.2707901053</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1556.903669041383</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J43" t="n">
-        <v>1868.487409693834</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K43" t="n">
         <v>1921.641060958496</v>
@@ -7590,22 +7590,22 @@
         <v>44.8</v>
       </c>
       <c r="T43" t="n">
-        <v>183.3756791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U43" t="n">
-        <v>380.4268717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V43" t="n">
-        <v>529.7482646830374</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W43" t="n">
-        <v>652.1391829427148</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X43" t="n">
-        <v>753.6699739669083</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.5792746459406</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="44">
@@ -7639,25 +7639,25 @@
         <v>44.8</v>
       </c>
       <c r="J44" t="n">
-        <v>65.95117127106482</v>
+        <v>138.2009049473324</v>
       </c>
       <c r="K44" t="n">
-        <v>620.3511712710648</v>
+        <v>692.6009049473324</v>
       </c>
       <c r="L44" t="n">
-        <v>1174.751171271065</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="M44" t="n">
-        <v>1685.6</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="N44" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2240</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2240</v>
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>275.3316144816847</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C45" t="n">
-        <v>264.1195817084329</v>
+        <v>387.8669114524009</v>
       </c>
       <c r="D45" t="n">
-        <v>264.1195817084329</v>
+        <v>387.8669114524009</v>
       </c>
       <c r="E45" t="n">
-        <v>264.1195817084329</v>
+        <v>387.8669114524009</v>
       </c>
       <c r="F45" t="n">
-        <v>264.1195817084329</v>
+        <v>44.8</v>
       </c>
       <c r="G45" t="n">
-        <v>264.1195817084329</v>
+        <v>44.8</v>
       </c>
       <c r="H45" t="n">
-        <v>264.1195817084329</v>
+        <v>44.8</v>
       </c>
       <c r="I45" t="n">
         <v>44.8</v>
@@ -7742,28 +7742,28 @@
         <v>1200.232420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>803.4393153922998</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>685.6979012866318</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T45" t="n">
-        <v>629.7809667234866</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U45" t="n">
-        <v>579.0634316121868</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V45" t="n">
-        <v>513.9011415197422</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W45" t="n">
-        <v>430.6959466613296</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X45" t="n">
-        <v>360.1275229791199</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y45" t="n">
-        <v>310.2372272557519</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="46">
@@ -7773,28 +7773,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.1258296400258</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.6278354584616</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.446979583462</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.775883794875</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.63685638681</v>
+        <v>1161.347639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.543422273696</v>
+        <v>1265.254204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.560007433093</v>
+        <v>1385.2707901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.192886369176</v>
+        <v>1556.903669041383</v>
       </c>
       <c r="J46" t="n">
         <v>1860.776627021628</v>
@@ -7827,22 +7827,22 @@
         <v>44.8</v>
       </c>
       <c r="T46" t="n">
-        <v>175.6648964865979</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.7160891248845</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>522.0374820108304</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W46" t="n">
-        <v>644.4284002705078</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X46" t="n">
-        <v>745.9591912947013</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.8684919737336</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
   </sheetData>
@@ -7973,16 +7973,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>914.6661680463578</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>863.2489580698352</v>
+        <v>847.6529984738759</v>
       </c>
       <c r="O2" t="n">
         <v>456.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>386.2870600406814</v>
       </c>
       <c r="Q2" t="n">
         <v>558.8226843274854</v>
@@ -8441,16 +8441,16 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
-        <v>370.4040404040406</v>
+        <v>387</v>
       </c>
       <c r="L8" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M8" t="n">
-        <v>930.2621276423173</v>
+        <v>931.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>863.2489580698352</v>
+        <v>848.6125944334717</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8678,25 +8678,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L11" t="n">
-        <v>186.1030891246556</v>
+        <v>259.0826180905825</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N11" t="n">
         <v>1037.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>630.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>560</v>
+        <v>303.0737001825673</v>
       </c>
       <c r="L14" t="n">
-        <v>138.3354305236337</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -9152,16 +9152,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>303.0737001825674</v>
+        <v>303.0737001825673</v>
       </c>
       <c r="L17" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>477.2489580698352</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O17" t="n">
         <v>70.24786957409245</v>
@@ -9404,10 +9404,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>303.360760223249</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>358.9257734521414</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L23" t="n">
-        <v>186.1030891246556</v>
+        <v>559.9999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,7 +9638,7 @@
         <v>1037.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>630.2478695740924</v>
+        <v>91.61268903981454</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
@@ -9860,10 +9860,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>56.40782571081238</v>
       </c>
       <c r="K26" t="n">
-        <v>186.1030891246556</v>
+        <v>560</v>
       </c>
       <c r="L26" t="n">
         <v>560</v>
@@ -10100,10 +10100,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>21.36481946572204</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="L29" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10118,7 +10118,7 @@
         <v>560.2870600406815</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,13 +10334,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>138.3354305236338</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10349,10 +10349,10 @@
         <v>1037.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>373.3215697566601</v>
       </c>
       <c r="P32" t="n">
-        <v>560.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10577,16 +10577,16 @@
         <v>560</v>
       </c>
       <c r="L35" t="n">
-        <v>560.0000000000001</v>
+        <v>186.1030891246556</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1037.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>212.3598766067635</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>56.40782571081238</v>
       </c>
       <c r="K38" t="n">
         <v>560</v>
       </c>
       <c r="L38" t="n">
-        <v>259.0826180905825</v>
+        <v>560</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>560.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>56.40782571081238</v>
+        <v>173.3784367687242</v>
       </c>
       <c r="K41" t="n">
         <v>560</v>
@@ -11057,7 +11057,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1037.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
         <v>70.24786957409245</v>
@@ -11066,7 +11066,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>56.40782571081238</v>
+        <v>129.3873546767392</v>
       </c>
       <c r="K44" t="n">
         <v>560</v>
@@ -11291,7 +11291,7 @@
         <v>560</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
         <v>1037.248958069835</v>
@@ -11303,7 +11303,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>716398.1223093561</v>
+        <v>716398.1223093562</v>
       </c>
     </row>
     <row r="3">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2038744.014658581</v>
+        <v>2038791.292234338</v>
       </c>
     </row>
     <row r="5">
@@ -26302,7 +26302,7 @@
         <v>1542736.874407429</v>
       </c>
       <c r="M2" t="n">
-        <v>1542736.874407428</v>
+        <v>1542736.874407429</v>
       </c>
       <c r="N2" t="n">
         <v>1542736.874407429</v>
@@ -26327,10 +26327,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="E3" t="n">
-        <v>341248</v>
+        <v>340896</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26351,10 +26351,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="M3" t="n">
-        <v>61248</v>
+        <v>60896</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570809.2415627229</v>
+        <v>572326.3960678478</v>
       </c>
       <c r="C4" t="n">
-        <v>568751.8817275827</v>
+        <v>570269.0362327078</v>
       </c>
       <c r="D4" t="n">
-        <v>566691.7309554147</v>
+        <v>568084.3396923635</v>
       </c>
       <c r="E4" t="n">
-        <v>542968.9204048133</v>
+        <v>544712.0690347301</v>
       </c>
       <c r="F4" t="n">
-        <v>541026.7377991641</v>
+        <v>542769.886429081</v>
       </c>
       <c r="G4" t="n">
-        <v>539081.8750543876</v>
+        <v>540825.0236843044</v>
       </c>
       <c r="H4" t="n">
-        <v>537134.3129511029</v>
+        <v>538877.4615810197</v>
       </c>
       <c r="I4" t="n">
-        <v>535184.0320195116</v>
+        <v>536927.1806494284</v>
       </c>
       <c r="J4" t="n">
-        <v>533231.0125346463</v>
+        <v>534974.1611645631</v>
       </c>
       <c r="K4" t="n">
-        <v>531275.2345115119</v>
+        <v>533018.3831414287</v>
       </c>
       <c r="L4" t="n">
-        <v>529316.6777000939</v>
+        <v>531059.8263300108</v>
       </c>
       <c r="M4" t="n">
-        <v>527355.3215802428</v>
+        <v>529098.4702101597</v>
       </c>
       <c r="N4" t="n">
-        <v>525391.145356436</v>
+        <v>527134.2939863527</v>
       </c>
       <c r="O4" t="n">
-        <v>523424.1279523973</v>
+        <v>525167.2765823142</v>
       </c>
       <c r="P4" t="n">
-        <v>521454.2480055793</v>
+        <v>523197.3966354961</v>
       </c>
     </row>
     <row r="5">
@@ -26431,7 +26431,7 @@
         <v>57096.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>57096.39999999999</v>
+        <v>57157.2</v>
       </c>
       <c r="E5" t="n">
         <v>63472.15</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>778959.2328447056</v>
+        <v>777442.0783395809</v>
       </c>
       <c r="C6" t="n">
-        <v>916888.5926798461</v>
+        <v>915371.4381747207</v>
       </c>
       <c r="D6" t="n">
-        <v>918948.7434520141</v>
+        <v>917143.3347150655</v>
       </c>
       <c r="E6" t="n">
-        <v>595047.8040026155</v>
+        <v>593656.6553726987</v>
       </c>
       <c r="F6" t="n">
-        <v>938237.9866082646</v>
+        <v>936494.837978348</v>
       </c>
       <c r="G6" t="n">
-        <v>940182.8493530414</v>
+        <v>938439.7007231246</v>
       </c>
       <c r="H6" t="n">
-        <v>942130.4114563259</v>
+        <v>940387.2628264091</v>
       </c>
       <c r="I6" t="n">
-        <v>944080.6923879172</v>
+        <v>942337.5437580004</v>
       </c>
       <c r="J6" t="n">
-        <v>530161.7118727824</v>
+        <v>528418.5632428656</v>
       </c>
       <c r="K6" t="n">
-        <v>947989.4898959169</v>
+        <v>946246.3412660001</v>
       </c>
       <c r="L6" t="n">
-        <v>949948.046707335</v>
+        <v>947852.8980774177</v>
       </c>
       <c r="M6" t="n">
-        <v>890661.4028271855</v>
+        <v>889270.2541972689</v>
       </c>
       <c r="N6" t="n">
-        <v>953873.5790509927</v>
+        <v>952130.430421076</v>
       </c>
       <c r="O6" t="n">
-        <v>675840.5964550312</v>
+        <v>674097.4478251148</v>
       </c>
       <c r="P6" t="n">
-        <v>957810.4764018496</v>
+        <v>956067.3277719327</v>
       </c>
     </row>
   </sheetData>
@@ -26865,7 +26865,7 @@
         <v>386</v>
       </c>
       <c r="D4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E4" t="n">
         <v>560</v>
@@ -27082,10 +27082,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -27106,10 +27106,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27323,10 +27323,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>367.4130086145855</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>367.4130086145855</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27524,13 +27524,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>197.8558048113095</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3083845693742</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27609,16 +27609,16 @@
         <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T4" t="n">
+        <v>227.9509150728214</v>
+      </c>
+      <c r="U4" t="n">
         <v>400</v>
       </c>
-      <c r="T4" t="n">
-        <v>210.0245665062577</v>
-      </c>
-      <c r="U4" t="n">
-        <v>150.9583912744579</v>
-      </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>385.1890253123776</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>117.4941682972701</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>367.4130086145855</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>151.3467752103375</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>200.5081550356338</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27797,7 +27797,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>161.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>14.21035976018675</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
@@ -27837,16 +27837,16 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>303.237924682272</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
@@ -27855,7 +27855,7 @@
         <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>356.8151162918375</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,7 +27882,7 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27894,10 +27894,10 @@
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>117.4941682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>363.5322086145854</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28043,16 +28043,16 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
+        <v>87.84297351553658</v>
+      </c>
+      <c r="V9" t="n">
+        <v>27.51066719152016</v>
+      </c>
+      <c r="W9" t="n">
         <v>400</v>
       </c>
-      <c r="V9" t="n">
-        <v>262.0384932613611</v>
-      </c>
-      <c r="W9" t="n">
-        <v>46.37314290982852</v>
-      </c>
       <c r="X9" t="n">
-        <v>33.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28068,16 +28068,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>388.646594649803</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28086,7 +28086,7 @@
         <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>386.9889853301057</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>400</v>
@@ -28159,13 +28159,13 @@
         <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="H11" t="n">
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>142.2349682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
         <v>350</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -28241,7 +28241,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>269.4903246609784</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28271,10 +28271,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="T12" t="n">
         <v>350</v>
@@ -28305,7 +28305,7 @@
         <v>350</v>
       </c>
       <c r="C13" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="D13" t="n">
         <v>350</v>
@@ -28317,7 +28317,7 @@
         <v>350</v>
       </c>
       <c r="G13" t="n">
-        <v>350</v>
+        <v>342.2113306341345</v>
       </c>
       <c r="H13" t="n">
         <v>350</v>
@@ -28396,7 +28396,7 @@
         <v>350</v>
       </c>
       <c r="G14" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="H14" t="n">
         <v>350</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>243.0324074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
         <v>350</v>
@@ -28463,7 +28463,7 @@
         <v>350</v>
       </c>
       <c r="C15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>347.9376868977026</v>
@@ -28523,13 +28523,13 @@
         <v>350</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X15" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="Y15" t="n">
-        <v>350</v>
+        <v>287.3222374745573</v>
       </c>
     </row>
     <row r="16">
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>243.0324074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
         <v>350</v>
@@ -28678,7 +28678,7 @@
         <v>350</v>
       </c>
       <c r="V17" t="n">
-        <v>350</v>
+        <v>342.1538086145856</v>
       </c>
       <c r="W17" t="n">
         <v>350</v>
@@ -28712,10 +28712,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>245.2298605360058</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
         <v>217.1263858913485</v>
@@ -28760,10 +28760,10 @@
         <v>350</v>
       </c>
       <c r="W18" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="X18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>142.2349682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>243.0324074428798</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28940,19 +28940,19 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>267.4280115586811</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343468</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
         <v>217.1263858913485</v>
@@ -29067,10 +29067,10 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U22" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="V22" t="n">
         <v>350</v>
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>342.1538086145855</v>
+        <v>350</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>243.0324074428798</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29189,10 +29189,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>136.6167105523269</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29225,10 +29225,10 @@
         <v>350</v>
       </c>
       <c r="T24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -29259,7 +29259,7 @@
         <v>350</v>
       </c>
       <c r="E25" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="F25" t="n">
         <v>350</v>
@@ -29307,7 +29307,7 @@
         <v>350</v>
       </c>
       <c r="U25" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="V25" t="n">
         <v>350</v>
@@ -29417,10 +29417,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>269.6305770343468</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>325.7395358750273</v>
@@ -29459,10 +29459,10 @@
         <v>350</v>
       </c>
       <c r="S27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="U27" t="n">
         <v>350</v>
@@ -29581,13 +29581,13 @@
         <v>350</v>
       </c>
       <c r="G29" t="n">
-        <v>342.1538086145855</v>
+        <v>350</v>
       </c>
       <c r="H29" t="n">
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29651,7 +29651,7 @@
         <v>350</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -29693,13 +29693,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>285.25992437226</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>350</v>
       </c>
       <c r="T30" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="U30" t="n">
         <v>350</v>
@@ -29730,7 +29730,7 @@
         <v>350</v>
       </c>
       <c r="D31" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="E31" t="n">
         <v>350</v>
@@ -29745,7 +29745,7 @@
         <v>350</v>
       </c>
       <c r="I31" t="n">
-        <v>350</v>
+        <v>342.2113306341345</v>
       </c>
       <c r="J31" t="n">
         <v>350</v>
@@ -29818,13 +29818,13 @@
         <v>350</v>
       </c>
       <c r="G32" t="n">
-        <v>342.1538086145855</v>
+        <v>350</v>
       </c>
       <c r="H32" t="n">
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29882,22 +29882,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>255.7338705714973</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>332.1680871864211</v>
@@ -29964,7 +29964,7 @@
         <v>350</v>
       </c>
       <c r="C34" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="D34" t="n">
         <v>350</v>
@@ -30015,7 +30015,7 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="U34" t="n">
         <v>350</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>142.2349682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
         <v>350</v>
       </c>
       <c r="X35" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="Y35" t="n">
         <v>350</v>
@@ -30131,7 +30131,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="G36" t="n">
         <v>325.7395358750273</v>
@@ -30164,16 +30164,16 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
       </c>
       <c r="T36" t="n">
-        <v>110.4015025650369</v>
+        <v>350</v>
       </c>
       <c r="U36" t="n">
         <v>350</v>
@@ -30198,10 +30198,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>350</v>
+        <v>342.2113306341345</v>
       </c>
       <c r="C37" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="D37" t="n">
         <v>350</v>
@@ -30295,10 +30295,10 @@
         <v>350</v>
       </c>
       <c r="H38" t="n">
-        <v>342.1538086145855</v>
+        <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30362,10 +30362,10 @@
         <v>350</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>277.9320215941726</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30410,7 +30410,7 @@
         <v>350</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U39" t="n">
         <v>350</v>
@@ -30419,7 +30419,7 @@
         <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="X39" t="n">
         <v>350</v>
@@ -30462,7 +30462,7 @@
         <v>350</v>
       </c>
       <c r="K40" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="L40" t="n">
         <v>350</v>
@@ -30504,7 +30504,7 @@
         <v>350</v>
       </c>
       <c r="Y40" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41">
@@ -30529,7 +30529,7 @@
         <v>350</v>
       </c>
       <c r="G41" t="n">
-        <v>342.1538086145855</v>
+        <v>350</v>
       </c>
       <c r="H41" t="n">
         <v>350</v>
@@ -30571,7 +30571,7 @@
         <v>350</v>
       </c>
       <c r="U41" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="V41" t="n">
         <v>350</v>
@@ -30614,7 +30614,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>154.448623365906</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30644,7 +30644,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30699,34 +30699,34 @@
         <v>350</v>
       </c>
       <c r="K43" t="n">
+        <v>350</v>
+      </c>
+      <c r="L43" t="n">
+        <v>350</v>
+      </c>
+      <c r="M43" t="n">
+        <v>350</v>
+      </c>
+      <c r="N43" t="n">
+        <v>350</v>
+      </c>
+      <c r="O43" t="n">
+        <v>350</v>
+      </c>
+      <c r="P43" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>350</v>
+      </c>
+      <c r="R43" t="n">
+        <v>350</v>
+      </c>
+      <c r="S43" t="n">
+        <v>350</v>
+      </c>
+      <c r="T43" t="n">
         <v>342.2113306341344</v>
-      </c>
-      <c r="L43" t="n">
-        <v>350</v>
-      </c>
-      <c r="M43" t="n">
-        <v>350</v>
-      </c>
-      <c r="N43" t="n">
-        <v>350</v>
-      </c>
-      <c r="O43" t="n">
-        <v>350</v>
-      </c>
-      <c r="P43" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>350</v>
-      </c>
-      <c r="R43" t="n">
-        <v>350</v>
-      </c>
-      <c r="S43" t="n">
-        <v>350</v>
-      </c>
-      <c r="T43" t="n">
-        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30833,7 +30833,7 @@
         <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>350</v>
+        <v>276.9584798124342</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30842,7 +30842,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>325.7395358750273</v>
@@ -30851,7 +30851,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30878,7 +30878,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>154.4486233659057</v>
+        <v>350</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -30933,7 +30933,7 @@
         <v>350</v>
       </c>
       <c r="J46" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="K46" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341344</v>
+        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34752,16 +34752,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>370.4040404040406</v>
-      </c>
-      <c r="N2" t="n">
-        <v>386</v>
       </c>
       <c r="O2" t="n">
         <v>386</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="Q2" t="n">
         <v>386</v>
@@ -34895,16 +34895,16 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>17.92634856656368</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>137.74537988227</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -35123,16 +35123,16 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>22.25701984531545</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>223.3665443798817</v>
@@ -35141,7 +35141,7 @@
         <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>68.29434249069446</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,7 +35168,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35180,10 +35180,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35220,16 +35220,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>370.4040404040406</v>
+        <v>387</v>
       </c>
       <c r="L8" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M8" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N8" t="n">
-        <v>386</v>
+        <v>371.3636363636364</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35354,16 +35354,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>103.1103765942475</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
@@ -35372,7 +35372,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>210.3555297099874</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>364.7310511640923</v>
@@ -35457,25 +35457,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L11" t="n">
-        <v>186.1030891246556</v>
+        <v>259.0826180905825</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>560</v>
       </c>
       <c r="O11" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35591,7 +35591,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C13" t="n">
-        <v>69.48608398608974</v>
+        <v>77.27475335195533</v>
       </c>
       <c r="D13" t="n">
         <v>64.46378194444452</v>
@@ -35603,7 +35603,7 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>104.95612715847</v>
+        <v>97.16745779260444</v>
       </c>
       <c r="H13" t="n">
         <v>121.2288738983814</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>560</v>
+        <v>303.0737001825673</v>
       </c>
       <c r="L14" t="n">
-        <v>138.3354305236337</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35931,16 +35931,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>303.0737001825674</v>
+        <v>303.0737001825673</v>
       </c>
       <c r="L17" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -36183,10 +36183,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>303.0737001825676</v>
+        <v>560</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>186.1030891246559</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36353,10 +36353,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U22" t="n">
-        <v>191.2529393596764</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V22" t="n">
         <v>150.8296897837838</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L23" t="n">
-        <v>186.1030891246556</v>
+        <v>559.9999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,7 +36417,7 @@
         <v>560</v>
       </c>
       <c r="O23" t="n">
-        <v>560</v>
+        <v>21.36481946572209</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36545,7 +36545,7 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E25" t="n">
-        <v>69.01909516304346</v>
+        <v>61.23042579717785</v>
       </c>
       <c r="F25" t="n">
         <v>75.61714403225807</v>
@@ -36593,7 +36593,7 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U25" t="n">
-        <v>191.2529393596764</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V25" t="n">
         <v>150.8296897837838</v>
@@ -36639,10 +36639,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>21.36481946572204</v>
       </c>
       <c r="K26" t="n">
-        <v>186.1030891246556</v>
+        <v>560</v>
       </c>
       <c r="L26" t="n">
         <v>560</v>
@@ -36879,10 +36879,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>21.36481946572204</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="L29" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36897,7 +36897,7 @@
         <v>560</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37016,7 +37016,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>56.67511257857893</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E31" t="n">
         <v>69.01909516304346</v>
@@ -37031,7 +37031,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I31" t="n">
-        <v>173.3665443798817</v>
+        <v>165.5778750140162</v>
       </c>
       <c r="J31" t="n">
         <v>314.7310511640923</v>
@@ -37113,13 +37113,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>138.3354305236338</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
@@ -37128,10 +37128,10 @@
         <v>560</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>303.0737001825676</v>
       </c>
       <c r="P32" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37250,7 +37250,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C34" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608974</v>
       </c>
       <c r="D34" t="n">
         <v>64.46378194444452</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>132.1867641278766</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
@@ -37356,16 +37356,16 @@
         <v>560</v>
       </c>
       <c r="L35" t="n">
-        <v>560.0000000000001</v>
+        <v>186.1030891246556</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
         <v>560</v>
       </c>
       <c r="O35" t="n">
-        <v>142.1120070326711</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37484,10 +37484,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705578</v>
       </c>
       <c r="C37" t="n">
-        <v>69.48608398608974</v>
+        <v>77.27475335195533</v>
       </c>
       <c r="D37" t="n">
         <v>64.46378194444452</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>395.2617303410664</v>
+        <v>21.36481946572204</v>
       </c>
       <c r="K38" t="n">
         <v>560</v>
       </c>
       <c r="L38" t="n">
-        <v>259.0826180905825</v>
+        <v>560</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P38" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37748,7 +37748,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299136</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37790,7 +37790,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y40" t="n">
-        <v>54.74597778467206</v>
+        <v>62.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37824,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>21.36481946572204</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="K41" t="n">
         <v>560</v>
@@ -37836,7 +37836,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -37845,7 +37845,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37985,7 +37985,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K43" t="n">
-        <v>53.69055683299136</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>21.36481946572204</v>
+        <v>94.3443484316489</v>
       </c>
       <c r="K44" t="n">
         <v>560</v>
@@ -38070,7 +38070,7 @@
         <v>560</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>560</v>
@@ -38082,7 +38082,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982266</v>
       </c>
       <c r="K46" t="n">
         <v>61.47922619885696</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278766</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
